--- a/Rental_Tracker_Demo.xlsx
+++ b/Rental_Tracker_Demo.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Rent due to date</t>
   </si>
   <si>
-    <t xml:space="preserve">Rent collected</t>
+    <t xml:space="preserve">Rent collected (excl. late fees)</t>
   </si>
   <si>
     <t xml:space="preserve">Collection rate</t>
@@ -183,7 +183,7 @@
     <t xml:space="preserve">Rent due to date (£)</t>
   </si>
   <si>
-    <t xml:space="preserve">Collected (£)</t>
+    <t xml:space="preserve">Collected incl. late fees (£)</t>
   </si>
   <si>
     <t xml:space="preserve">Arrears (£)</t>
@@ -1164,7 +1164,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Collected (£)</c:v>
+                  <c:v>Collected incl. late fees (£)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
